--- a/test/excel/parts/struct-held/copy-b2-d6.xlsx
+++ b/test/excel/parts/struct-held/copy-b2-d6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fparts-11941/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-29694/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BBB07FE-6468-5A4E-A3D7-CDA116749BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A03936C4-F314-4941-B551-63C8E5705BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{0E3F671F-2F97-2245-A49A-E381D36CCB0B}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{D0043E1B-027E-EF45-906A-C3F4B4C16188}">
       <text>
         <r>
           <rPr>
@@ -70,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{6F899A0A-1A67-494E-BB9E-C64413D1A9E2}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{D200D59B-ACF4-7445-96E4-E857D1B76244}">
       <text>
         <r>
           <rPr>
@@ -569,9 +569,9 @@
     <hyperlink ref="B3" r:id="rId1" tooltip="B3" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" location="S!A1" display="to A1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D6" location="'T'!A1" display="to T" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F11" r:id="rId2" tooltip="B3" xr:uid="{47C72B9F-C4B3-AC48-B6FA-331213DDE087}"/>
-    <hyperlink ref="G13" location="S!A1" display="to A1" xr:uid="{812FDBEA-664C-404F-A77D-24ABA60346E5}"/>
-    <hyperlink ref="H14" location="'T'!A1" display="to T" xr:uid="{1819A35F-B193-7A49-A442-EFF26E6B27A7}"/>
+    <hyperlink ref="F11" r:id="rId2" tooltip="B3" xr:uid="{0F166A54-64A0-1042-AB4A-AE25C879F8BE}"/>
+    <hyperlink ref="G13" location="S!A1" display="to A1" xr:uid="{D613049F-FB7D-2E45-9E6E-A5C2B2F4EA51}"/>
+    <hyperlink ref="H14" location="'T'!A1" display="to T" xr:uid="{B0D1C3EB-FB29-D848-AB7A-4729F8997BD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
